--- a/data/patients_records.xlsx
+++ b/data/patients_records.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:AB3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -424,72 +424,265 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Booking Ref</v>
+        <v>bookingRef</v>
       </c>
       <c r="B1" t="str">
-        <v>Booking Date</v>
+        <v>bookingDate</v>
       </c>
       <c r="C1" t="str">
-        <v>Patient Name</v>
+        <v>patientName</v>
       </c>
       <c r="D1" t="str">
-        <v>First Name</v>
+        <v>firstName</v>
       </c>
       <c r="E1" t="str">
-        <v>Last Name</v>
+        <v>lastName</v>
       </c>
       <c r="F1" t="str">
-        <v>Phone</v>
+        <v>phone</v>
       </c>
       <c r="G1" t="str">
-        <v>Email</v>
+        <v>email</v>
       </c>
       <c r="H1" t="str">
-        <v>Date of Birth</v>
+        <v>dob</v>
       </c>
       <c r="I1" t="str">
-        <v>Patient Type</v>
+        <v>patientType</v>
       </c>
       <c r="J1" t="str">
-        <v>Branch Name</v>
+        <v>branchName</v>
       </c>
       <c r="K1" t="str">
-        <v>Branch Address</v>
+        <v>branchAddress</v>
       </c>
       <c r="L1" t="str">
-        <v>Branch Phone</v>
+        <v>branchPhone</v>
       </c>
       <c r="M1" t="str">
-        <v>Treatment Name</v>
+        <v>branchId</v>
       </c>
       <c r="N1" t="str">
-        <v>Duration</v>
+        <v>treatmentName</v>
       </c>
       <c r="O1" t="str">
-        <v>Estimated Fee</v>
+        <v>treatmentDuration</v>
       </c>
       <c r="P1" t="str">
-        <v>Dentist Name</v>
+        <v>estimatedFee</v>
       </c>
       <c r="Q1" t="str">
-        <v>Specialization</v>
+        <v>doctorName</v>
       </c>
       <c r="R1" t="str">
-        <v>Appointment Date</v>
+        <v>doctorSpecialization</v>
       </c>
       <c r="S1" t="str">
-        <v>Appointment Time</v>
+        <v>appointmentDate</v>
       </c>
       <c r="T1" t="str">
-        <v>Notes</v>
+        <v>appointmentTime</v>
       </c>
       <c r="U1" t="str">
-        <v>Status</v>
+        <v>notes</v>
+      </c>
+      <c r="V1" t="str">
+        <v>status</v>
+      </c>
+      <c r="W1" t="str">
+        <v>paymentMode</v>
+      </c>
+      <c r="X1" t="str">
+        <v>paymentStatus</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>paymentRef</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>amountPaidNow</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>amountRemaining</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>attachmentName</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SCWN2MG</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-09-18 10:24</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Karan Kshirsagar</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Kshirsagar</v>
+      </c>
+      <c r="F2" t="str">
+        <v>9527050086</v>
+      </c>
+      <c r="G2" t="str">
+        <v>karanrk2005@gmail.com</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Not specified</v>
+      </c>
+      <c r="I2" t="str">
+        <v>New patient</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Smart Dental Clinic – Downtown Central (Main)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>102 Wellness Plaza, Dental Street, Medical Hub, Central City - 400001</v>
+      </c>
+      <c r="L2" t="str">
+        <v>+91 98765 00000</v>
+      </c>
+      <c r="M2" t="str">
+        <v>branch-1</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Composite Tooth-Colored Filling</v>
+      </c>
+      <c r="O2" t="str">
+        <v>35 min</v>
+      </c>
+      <c r="P2" t="str">
+        <v>₹1,000 – ₹2,200</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Dr. Vikram Shah</v>
+      </c>
+      <c r="R2" t="str">
+        <v>General Dental Surgeon</v>
+      </c>
+      <c r="S2" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="T2" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="U2" t="str">
+        <v>None</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Pay at Clinic Counter</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Pending at Clinic Counter</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>₹0</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>₹1,000 – ₹2,200</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SCXOCCJ</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-09-18 09:55</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Karan Kshirsagar</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Kshirsagar</v>
+      </c>
+      <c r="F3" t="str">
+        <v>9527050086</v>
+      </c>
+      <c r="G3" t="str">
+        <v>karanrk2005@gmail.com</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Not specified</v>
+      </c>
+      <c r="I3" t="str">
+        <v>New patient</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Smart Dental Clinic – Downtown Central (Main)</v>
+      </c>
+      <c r="K3" t="str">
+        <v>102 Wellness Plaza, Dental Street, Medical Hub, Central City - 400001</v>
+      </c>
+      <c r="L3" t="str">
+        <v>+91 98765 00000</v>
+      </c>
+      <c r="M3" t="str">
+        <v>branch-1</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Tooth Sensitivity Relief</v>
+      </c>
+      <c r="O3" t="str">
+        <v>30 min</v>
+      </c>
+      <c r="P3" t="str">
+        <v>₹600 – ₹1,500</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Dr. Vikram Shah</v>
+      </c>
+      <c r="R3" t="str">
+        <v>General Dental Surgeon</v>
+      </c>
+      <c r="S3" t="str">
+        <v>2026-09-19</v>
+      </c>
+      <c r="T3" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U3" t="str">
+        <v>None</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Advance Paid (₹600)</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Advance Paid (₹600) · Remaining ₹0</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>₹600</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>₹0</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>None</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/patients_records.xlsx
+++ b/data/patients_records.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Patient Records" sheetId="1" r:id="rId1"/>
+    <sheet name="Records (September 2026)" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AC5"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -507,13 +507,16 @@
       <c r="AB1" t="str">
         <v>attachmentName</v>
       </c>
+      <c r="AC1" t="str">
+        <v>reminder2hSent</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SCWN2MG</v>
+        <v>SCMX2V4</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-18 10:24</v>
+        <v>2026-09-28 07:38</v>
       </c>
       <c r="C2" t="str">
         <v>Karan Kshirsagar</v>
@@ -549,13 +552,13 @@
         <v>branch-1</v>
       </c>
       <c r="N2" t="str">
-        <v>Composite Tooth-Colored Filling</v>
+        <v>Dental X-Ray (OPG &amp; Bitewing)</v>
       </c>
       <c r="O2" t="str">
-        <v>35 min</v>
+        <v>15 min</v>
       </c>
       <c r="P2" t="str">
-        <v>₹1,000 – ₹2,200</v>
+        <v>₹600 – ₹1,000</v>
       </c>
       <c r="Q2" t="str">
         <v>Dr. Vikram Shah</v>
@@ -564,31 +567,31 @@
         <v>General Dental Surgeon</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-30</v>
       </c>
       <c r="T2" t="str">
-        <v>10:30 AM</v>
+        <v>5:30 PM</v>
       </c>
       <c r="U2" t="str">
-        <v>None</v>
+        <v>Updated from admin edit modal test</v>
       </c>
       <c r="V2" t="str">
         <v>Confirmed</v>
       </c>
       <c r="W2" t="str">
-        <v>Pay at Clinic Counter</v>
+        <v>Advance Paid (₹600)</v>
       </c>
       <c r="X2" t="str">
-        <v>Pending at Clinic Counter</v>
+        <v>Advance Paid (₹600) · Remaining ₹0</v>
       </c>
       <c r="Y2" t="str">
         <v>N/A</v>
       </c>
       <c r="Z2" t="str">
+        <v>₹600</v>
+      </c>
+      <c r="AA2" t="str">
         <v>₹0</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>₹1,000 – ₹2,200</v>
       </c>
       <c r="AB2" t="str">
         <v>None</v>
@@ -596,22 +599,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SCXOCCJ</v>
+        <v>SCJXXRQ</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-18 09:55</v>
+        <v>2026-09-28 07:38</v>
       </c>
       <c r="C3" t="str">
-        <v>Karan Kshirsagar</v>
+        <v>piu  kadam</v>
       </c>
       <c r="D3" t="str">
-        <v>Karan</v>
+        <v>piu</v>
       </c>
       <c r="E3" t="str">
-        <v>Kshirsagar</v>
+        <v xml:space="preserve"> kadam</v>
       </c>
       <c r="F3" t="str">
-        <v>9527050086</v>
+        <v>12345674</v>
       </c>
       <c r="G3" t="str">
         <v>karanrk2005@gmail.com</v>
@@ -635,22 +638,22 @@
         <v>branch-1</v>
       </c>
       <c r="N3" t="str">
-        <v>Tooth Sensitivity Relief</v>
+        <v>Consultation &amp; Checkup</v>
       </c>
       <c r="O3" t="str">
         <v>30 min</v>
       </c>
       <c r="P3" t="str">
-        <v>₹600 – ₹1,500</v>
+        <v>₹300 – ₹800</v>
       </c>
       <c r="Q3" t="str">
-        <v>Dr. Vikram Shah</v>
+        <v>Dr. Priya Mehta</v>
       </c>
       <c r="R3" t="str">
-        <v>General Dental Surgeon</v>
+        <v>General &amp; Preventive Dentistry</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-28</v>
       </c>
       <c r="T3" t="str">
         <v>10:00 AM</v>
@@ -662,27 +665,202 @@
         <v>Confirmed</v>
       </c>
       <c r="W3" t="str">
-        <v>Advance Paid (₹600)</v>
+        <v>Advance Paid (₹300)</v>
       </c>
       <c r="X3" t="str">
-        <v>Advance Paid (₹600) · Remaining ₹0</v>
+        <v>Advance Paid (₹300) · Remaining ₹0</v>
       </c>
       <c r="Y3" t="str">
         <v>N/A</v>
       </c>
       <c r="Z3" t="str">
-        <v>₹600</v>
+        <v>₹300</v>
       </c>
       <c r="AA3" t="str">
         <v>₹0</v>
       </c>
       <c r="AB3" t="str">
+        <v>None</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SCWN2MG</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-09-18 10:24</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Karan Kshirsagar</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Kshirsagar</v>
+      </c>
+      <c r="F4" t="str">
+        <v>9527050086</v>
+      </c>
+      <c r="G4" t="str">
+        <v>karanrk2005@gmail.com</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Not specified</v>
+      </c>
+      <c r="I4" t="str">
+        <v>New patient</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Smart Dental Clinic – Downtown Central (Main)</v>
+      </c>
+      <c r="K4" t="str">
+        <v>102 Wellness Plaza, Dental Street, Medical Hub, Central City - 400001</v>
+      </c>
+      <c r="L4" t="str">
+        <v>+91 98765 00000</v>
+      </c>
+      <c r="M4" t="str">
+        <v>branch-1</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Composite Tooth-Colored Filling</v>
+      </c>
+      <c r="O4" t="str">
+        <v>35 min</v>
+      </c>
+      <c r="P4" t="str">
+        <v>₹1,000 – ₹2,200</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Dr. Vikram Shah</v>
+      </c>
+      <c r="R4" t="str">
+        <v>General Dental Surgeon</v>
+      </c>
+      <c r="S4" t="str">
+        <v>2026-09-18</v>
+      </c>
+      <c r="T4" t="str">
+        <v>10:30 AM</v>
+      </c>
+      <c r="U4" t="str">
+        <v>None</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Pay at Clinic Counter</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Pending at Clinic Counter</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>₹0</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>₹1,000 – ₹2,200</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SCXOCCJ</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-09-18 09:55</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Karan Kshirsagar</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Karan</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Kshirsagar</v>
+      </c>
+      <c r="F5" t="str">
+        <v>9527050086</v>
+      </c>
+      <c r="G5" t="str">
+        <v>karanrk2005@gmail.com</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Not specified</v>
+      </c>
+      <c r="I5" t="str">
+        <v>New patient</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Smart Dental Clinic – Downtown Central (Main)</v>
+      </c>
+      <c r="K5" t="str">
+        <v>102 Wellness Plaza, Dental Street, Medical Hub, Central City - 400001</v>
+      </c>
+      <c r="L5" t="str">
+        <v>+91 98765 00000</v>
+      </c>
+      <c r="M5" t="str">
+        <v>branch-1</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Tooth Sensitivity Relief</v>
+      </c>
+      <c r="O5" t="str">
+        <v>30 min</v>
+      </c>
+      <c r="P5" t="str">
+        <v>₹600 – ₹1,500</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Dr. Vikram Shah</v>
+      </c>
+      <c r="R5" t="str">
+        <v>General Dental Surgeon</v>
+      </c>
+      <c r="S5" t="str">
+        <v>2026-09-19</v>
+      </c>
+      <c r="T5" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U5" t="str">
+        <v>None</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Confirmed</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Advance Paid (₹600)</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Advance Paid (₹600) · Remaining ₹0</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>₹600</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>₹0</v>
+      </c>
+      <c r="AB5" t="str">
         <v>None</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC5"/>
   </ignoredErrors>
 </worksheet>
 </file>